--- a/fixtures/xlsx/output-reopen/s8-7e3g-wps-spreadsheets.xlsx
+++ b/fixtures/xlsx/output-reopen/s8-7e3g-wps-spreadsheets.xlsx
@@ -776,7 +776,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="8" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46233.0666666667" recordCount="16">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="8" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46233.0762384259" recordCount="16">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:E17" sheet="Source"/>
   </cacheSource>
